--- a/Data/EXCEL/Transfer/salemon/202206/6810-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6810-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58686652-0040-4252-B2CB-7CB2D4DEA6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF86C92D-5EF9-47AB-91B8-7713F336E028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6810-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,22 +1218,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="6" width="10.75" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="10.75" customWidth="1"/>
-    <col min="10" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="10.25" customWidth="1"/>
-    <col min="13" max="13" width="12.375" customWidth="1"/>
-    <col min="14" max="14" width="10.75" customWidth="1"/>
-    <col min="15" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="12.375" customWidth="1"/>
-    <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="6" width="11.75" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="11.75" customWidth="1"/>
+    <col min="10" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="11.25" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="11.25" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1386,52 +1386,52 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7">
-        <v>40</v>
+        <v>38.950000000000003</v>
       </c>
       <c r="D5" s="7">
-        <v>42.55</v>
+        <v>43.65</v>
       </c>
       <c r="E5" s="7">
-        <v>37.75</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="F5" s="8">
-        <v>1</v>
+        <v>-1.05</v>
       </c>
       <c r="G5" s="8">
-        <v>2.56</v>
+        <v>-2.62</v>
       </c>
       <c r="H5" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="I5" s="8">
-        <v>950</v>
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="I5" s="10">
+        <v>436.9</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K5" s="9">
-        <v>6.0000000000000001E-3</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M5" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="N5" s="8">
-        <v>950</v>
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="N5" s="10">
+        <v>436.9</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="9">
-        <v>6.0000000000000001E-3</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="Q5" s="9" t="s">
         <v>17</v>
@@ -1439,52 +1439,52 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>41.05</v>
+        <v>39</v>
       </c>
       <c r="C6" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="7">
-        <v>42.65</v>
+        <v>42.55</v>
       </c>
       <c r="E6" s="7">
-        <v>37.1</v>
+        <v>37.75</v>
       </c>
       <c r="F6" s="10">
-        <v>-2.0499999999999998</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10">
-        <v>-4.99</v>
+        <v>2.56</v>
       </c>
       <c r="H6" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="8">
-        <v>166.7</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="I6" s="10">
+        <v>950</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="9">
-        <v>5.1999999999999998E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="N6" s="8">
-        <v>166.7</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="N6" s="10">
+        <v>950</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P6" s="9">
-        <v>5.1999999999999998E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q6" s="9" t="s">
         <v>17</v>
@@ -1492,52 +1492,52 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>43.95</v>
+        <v>41.05</v>
       </c>
       <c r="C7" s="7">
-        <v>41.05</v>
+        <v>39</v>
       </c>
       <c r="D7" s="7">
-        <v>45.2</v>
+        <v>42.65</v>
       </c>
       <c r="E7" s="7">
-        <v>38.85</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-2.9</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-6.6</v>
+        <v>37.1</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-2.0499999999999998</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-4.99</v>
       </c>
       <c r="H7" s="9">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="I7" s="10">
-        <v>-95.6</v>
+        <v>166.7</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="9">
-        <v>5.1000000000000004E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M7" s="9">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="N7" s="10">
-        <v>-95.6</v>
+        <v>166.7</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="9">
-        <v>5.1000000000000004E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>17</v>
@@ -1545,31 +1545,31 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>42.15</v>
+        <v>43.95</v>
       </c>
       <c r="C8" s="7">
-        <v>43.95</v>
+        <v>41.05</v>
       </c>
       <c r="D8" s="7">
-        <v>49.4</v>
+        <v>45.2</v>
       </c>
       <c r="E8" s="7">
-        <v>40.15</v>
+        <v>38.85</v>
       </c>
       <c r="F8" s="8">
-        <v>1.8</v>
+        <v>-2.9</v>
       </c>
       <c r="G8" s="8">
-        <v>4.2699999999999996</v>
+        <v>-6.6</v>
       </c>
       <c r="H8" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="I8" s="10">
-        <v>-84.5</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <v>-95.6</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>17</v>
@@ -1581,10 +1581,10 @@
         <v>17</v>
       </c>
       <c r="M8" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="N8" s="10">
-        <v>-84.5</v>
+        <v>0</v>
+      </c>
+      <c r="N8" s="8">
+        <v>-95.6</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>17</v>
@@ -1598,52 +1598,52 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>41.15</v>
+        <v>42.15</v>
       </c>
       <c r="C9" s="7">
-        <v>42.15</v>
+        <v>43.95</v>
       </c>
       <c r="D9" s="7">
-        <v>45</v>
+        <v>49.4</v>
       </c>
       <c r="E9" s="7">
-        <v>37.85</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8">
-        <v>2.4300000000000002</v>
+        <v>40.15</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="G9" s="10">
+        <v>4.2699999999999996</v>
       </c>
       <c r="H9" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="I9" s="8">
-        <v>212.8</v>
+        <v>-84.5</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K9" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M9" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="N9" s="8">
-        <v>212.8</v>
+        <v>-84.5</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P9" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="Q9" s="9" t="s">
         <v>17</v>
@@ -1651,52 +1651,52 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>40.85</v>
+        <v>41.15</v>
       </c>
       <c r="C10" s="7">
-        <v>41.15</v>
+        <v>42.15</v>
       </c>
       <c r="D10" s="7">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E10" s="7">
-        <v>38.549999999999997</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0.73</v>
+        <v>37.85</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>2.4300000000000002</v>
       </c>
       <c r="H10" s="9">
-        <v>1.4E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I10" s="10">
-        <v>-68</v>
+        <v>212.8</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K10" s="9">
-        <v>8.6999999999999994E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M10" s="9">
-        <v>1.4E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N10" s="10">
-        <v>-68</v>
+        <v>212.8</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P10" s="9">
-        <v>8.6999999999999994E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="Q10" s="9" t="s">
         <v>17</v>
@@ -1704,52 +1704,52 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>22.6</v>
+        <v>40.85</v>
       </c>
       <c r="C11" s="7">
-        <v>40.85</v>
+        <v>41.15</v>
       </c>
       <c r="D11" s="7">
-        <v>46.3</v>
+        <v>60</v>
       </c>
       <c r="E11" s="7">
-        <v>19.8</v>
-      </c>
-      <c r="F11" s="8">
-        <v>18.25</v>
-      </c>
-      <c r="G11" s="8">
-        <v>80.75</v>
+        <v>38.549999999999997</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.73</v>
       </c>
       <c r="H11" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="I11" s="8">
-        <v>100</v>
+        <v>-68</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K11" s="9">
-        <v>7.3000000000000001E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M11" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="N11" s="8">
-        <v>100</v>
+        <v>-68</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P11" s="9">
-        <v>7.3000000000000001E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="Q11" s="9" t="s">
         <v>17</v>
@@ -1757,52 +1757,52 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>24.85</v>
+        <v>22.6</v>
       </c>
       <c r="C12" s="7">
-        <v>22.6</v>
+        <v>40.85</v>
       </c>
       <c r="D12" s="7">
-        <v>27</v>
+        <v>46.3</v>
       </c>
       <c r="E12" s="7">
-        <v>18.8</v>
+        <v>19.8</v>
       </c>
       <c r="F12" s="10">
-        <v>-2.25</v>
+        <v>18.25</v>
       </c>
       <c r="G12" s="10">
-        <v>-9.0500000000000007</v>
+        <v>80.75</v>
       </c>
       <c r="H12" s="9">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>17</v>
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="I12" s="10">
+        <v>100</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="9">
-        <v>2.8999999999999998E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M12" s="9">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>17</v>
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="N12" s="10">
+        <v>100</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P12" s="9">
-        <v>2.8999999999999998E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="Q12" s="9" t="s">
         <v>17</v>
@@ -1810,52 +1810,52 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>20.5</v>
+        <v>24.85</v>
       </c>
       <c r="C13" s="7">
-        <v>24.85</v>
+        <v>22.6</v>
       </c>
       <c r="D13" s="7">
-        <v>29.6</v>
+        <v>27</v>
       </c>
       <c r="E13" s="7">
-        <v>17.2</v>
+        <v>18.8</v>
       </c>
       <c r="F13" s="8">
-        <v>4.3499999999999996</v>
+        <v>-2.25</v>
       </c>
       <c r="G13" s="8">
-        <v>21.22</v>
+        <v>-9.0500000000000007</v>
       </c>
       <c r="H13" s="9">
-        <v>0</v>
-      </c>
-      <c r="I13" s="10">
-        <v>-100</v>
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="9">
-        <v>8.0000000000000004E-4</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M13" s="9">
-        <v>0</v>
-      </c>
-      <c r="N13" s="10">
-        <v>-100</v>
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P13" s="9">
-        <v>8.0000000000000004E-4</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="Q13" s="9" t="s">
         <v>17</v>
@@ -1863,31 +1863,31 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="C14" s="7">
-        <v>20.5</v>
+        <v>24.85</v>
       </c>
       <c r="D14" s="7">
-        <v>54</v>
+        <v>29.6</v>
       </c>
       <c r="E14" s="7">
-        <v>20.05</v>
+        <v>17.2</v>
       </c>
       <c r="F14" s="10">
-        <v>-2.8</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="G14" s="10">
-        <v>-12.02</v>
+        <v>21.22</v>
       </c>
       <c r="H14" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-100</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>17</v>
@@ -1899,10 +1899,10 @@
         <v>17</v>
       </c>
       <c r="M14" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <v>-100</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>17</v>
@@ -1916,28 +1916,28 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>17</v>
+        <v>44409</v>
+      </c>
+      <c r="B15" s="7">
+        <v>23.3</v>
+      </c>
+      <c r="C15" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="D15" s="7">
+        <v>54</v>
+      </c>
+      <c r="E15" s="7">
+        <v>20.05</v>
+      </c>
+      <c r="F15" s="8">
+        <v>-2.8</v>
+      </c>
+      <c r="G15" s="8">
+        <v>-12.02</v>
       </c>
       <c r="H15" s="9">
-        <v>0</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>17</v>
@@ -1946,13 +1946,13 @@
         <v>17</v>
       </c>
       <c r="K15" s="9">
-        <v>0</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="L15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M15" s="9">
-        <v>0</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>17</v>
@@ -1961,7 +1961,7 @@
         <v>17</v>
       </c>
       <c r="P15" s="9">
-        <v>0</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q15" s="9" t="s">
         <v>17</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2128,7 +2128,7 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>17</v>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>17</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -2393,54 +2393,107 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
+        <v>44136</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P24" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
         <v>44105</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="9">
-        <v>0</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="9">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="9">
-        <v>0</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P24" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="9" t="s">
+      <c r="B25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="9">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25" s="9">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P25" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="9" t="s">
         <v>17</v>
       </c>
     </row>
